--- a/docs/dimensiuni-reale.xlsx
+++ b/docs/dimensiuni-reale.xlsx
@@ -25,25 +25,25 @@
     <t>Dimensiune</t>
   </si>
   <si>
-    <t>L acum</t>
-  </si>
-  <si>
-    <t>l acum</t>
-  </si>
-  <si>
-    <t>H acum</t>
+    <t>Lungime acum</t>
+  </si>
+  <si>
+    <t>Latime acum</t>
+  </si>
+  <si>
+    <t>Inaltime acum</t>
   </si>
   <si>
     <t>Din import?</t>
   </si>
   <si>
-    <t>L REAL  ←</t>
-  </si>
-  <si>
-    <t>l REAL  ←</t>
-  </si>
-  <si>
-    <t>H REAL  ←</t>
+    <t>Lungime REALA  ←</t>
+  </si>
+  <si>
+    <t>Latime REALA  ←</t>
+  </si>
+  <si>
+    <t>Inaltime REALA  ←</t>
   </si>
   <si>
     <t>Produs finit în SAGA</t>

--- a/docs/dimensiuni-reale.xlsx
+++ b/docs/dimensiuni-reale.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="290">
   <si>
     <t>Model</t>
   </si>
@@ -52,39 +52,54 @@
     <t>Bonuri</t>
   </si>
   <si>
-    <t>C3-SORIA</t>
-  </si>
-  <si>
-    <t>C3 SORIA</t>
+    <t>CANAPEA-ALDA-1-54</t>
+  </si>
+  <si>
+    <t>CANAPEA ALDA 1.54</t>
   </si>
   <si>
     <t>CANAPEA</t>
   </si>
   <si>
-    <t>123</t>
+    <t>STANDARD</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>00021308  CANAPEA SORIA 1500/1900 R</t>
-  </si>
-  <si>
-    <t>STANDARD</t>
-  </si>
-  <si>
     <t>DA — valoare de umplutură</t>
   </si>
   <si>
+    <t>00024650  CANAPEA ALDA 1.54</t>
+  </si>
+  <si>
+    <t>CANAPEA-ALDO</t>
+  </si>
+  <si>
+    <t>CANAPEA ALDO</t>
+  </si>
+  <si>
+    <t>00021262  CANAPEA ALDO</t>
+  </si>
+  <si>
+    <t>CANAPEA-ALDO-DUBLA</t>
+  </si>
+  <si>
+    <t>CANAPEA ALDO DUBLA</t>
+  </si>
+  <si>
+    <t>00023168  CANAPEA ALDO DUBLA</t>
+  </si>
+  <si>
+    <t>CANAPEA-ALMA-1200</t>
+  </si>
+  <si>
+    <t>CANAPEA ALMA 1200</t>
+  </si>
+  <si>
     <t>— nelegat —</t>
   </si>
   <si>
-    <t>CANAPEA-ALMA-1200</t>
-  </si>
-  <si>
-    <t>CANAPEA ALMA 1200</t>
-  </si>
-  <si>
     <t>CANAPEA-ATLAS</t>
   </si>
   <si>
@@ -94,6 +109,24 @@
     <t>00013384  CANAPEA ATLAS</t>
   </si>
   <si>
+    <t>CANAPEA-BELLA</t>
+  </si>
+  <si>
+    <t>CANAPEA BELLA</t>
+  </si>
+  <si>
+    <t>00025254  CANAPEA BELLA</t>
+  </si>
+  <si>
+    <t>CANAPEA-CHESTERFIELD-II</t>
+  </si>
+  <si>
+    <t>CANAPEA CHESTERFIELD II</t>
+  </si>
+  <si>
+    <t>00016668  CANAPEA CHESTERFIELD II</t>
+  </si>
+  <si>
     <t>CANAPEA-CORINA</t>
   </si>
   <si>
@@ -103,6 +136,24 @@
     <t>00000199  CANAPEA CORINA</t>
   </si>
   <si>
+    <t>CANAPEA-CORINA-E-M</t>
+  </si>
+  <si>
+    <t>CANAPEA CORINA E+M</t>
+  </si>
+  <si>
+    <t>00005884  CANAPEA CORINA E+M</t>
+  </si>
+  <si>
+    <t>CANAPEA-CORINA-EFLEX</t>
+  </si>
+  <si>
+    <t>CANAPEA CORINA EFLEX</t>
+  </si>
+  <si>
+    <t>00011675  CANAPEA CORINA EFLEX</t>
+  </si>
+  <si>
     <t>CANAPEA-CORINA-II</t>
   </si>
   <si>
@@ -112,12 +163,57 @@
     <t>00001382  CANAPEA CORINA  II 1300</t>
   </si>
   <si>
+    <t>CANAPEA-CORINA-R-M</t>
+  </si>
+  <si>
+    <t>CANAPEA CORINA R+M</t>
+  </si>
+  <si>
+    <t>00004919  CANAPEA CORINA R+M</t>
+  </si>
+  <si>
+    <t>CANAPEA-CUBICA</t>
+  </si>
+  <si>
+    <t>CANAPEA CUBICA</t>
+  </si>
+  <si>
+    <t>00014415  CANAPEA CUBICA</t>
+  </si>
+  <si>
     <t>CANAPEA-DUBLA-CUBIC</t>
   </si>
   <si>
     <t>CANAPEA DUBLA CUBIC</t>
   </si>
   <si>
+    <t>CANAPEA-ECO</t>
+  </si>
+  <si>
+    <t>CANAPEA ECO</t>
+  </si>
+  <si>
+    <t>00000489  CANAPEA ECO</t>
+  </si>
+  <si>
+    <t>CANAPEA-ECO-EFLEX</t>
+  </si>
+  <si>
+    <t>CANAPEA ECO EFLEX</t>
+  </si>
+  <si>
+    <t>00020245  CANAPEA ECO EFLEX</t>
+  </si>
+  <si>
+    <t>CANAPEA-FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA FIXA</t>
+  </si>
+  <si>
+    <t>00000337  CANAPEA FIXA</t>
+  </si>
+  <si>
     <t>CANAPEA-KARINA</t>
   </si>
   <si>
@@ -127,18 +223,96 @@
     <t>00002422  CANAPEA KARINA</t>
   </si>
   <si>
+    <t>CANAPEA-KARINA-R-M</t>
+  </si>
+  <si>
+    <t>CANAPEA KARINA R+M</t>
+  </si>
+  <si>
+    <t>00005885  CANAPEA KARINA R+M</t>
+  </si>
+  <si>
     <t>CANAPEA-MARIA</t>
   </si>
   <si>
     <t>CANAPEA MARIA</t>
   </si>
   <si>
-    <t>1234</t>
-  </si>
-  <si>
     <t>00000207  CANAPEA MARIA</t>
   </si>
   <si>
+    <t>CANAPEA-MARIA-FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA MARIA FIXA</t>
+  </si>
+  <si>
+    <t>00016022  CANAPEA MARIA FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA-MARIA-SPATAR</t>
+  </si>
+  <si>
+    <t>CANAPEA MARIA SPATAR</t>
+  </si>
+  <si>
+    <t>00006926  CANAPEA MARIA SPATAR</t>
+  </si>
+  <si>
+    <t>CANAPEA-MONA</t>
+  </si>
+  <si>
+    <t>CANAPEA MONA</t>
+  </si>
+  <si>
+    <t>00008204  CANAPEA MONA</t>
+  </si>
+  <si>
+    <t>CANAPEA-ROBERT</t>
+  </si>
+  <si>
+    <t>CANAPEA ROBERT</t>
+  </si>
+  <si>
+    <t>00000692  CANAPEA ROBERT</t>
+  </si>
+  <si>
+    <t>CANAPEA-SONIA</t>
+  </si>
+  <si>
+    <t>CANAPEA SONIA</t>
+  </si>
+  <si>
+    <t>00019569  CANAPEA SONIA</t>
+  </si>
+  <si>
+    <t>CANAPEA-SORIA</t>
+  </si>
+  <si>
+    <t>CANAPEA SORIA</t>
+  </si>
+  <si>
+    <t>00008608  CANAPEA SORIA</t>
+  </si>
+  <si>
+    <t>CANAPEA-SORIA-DUBLA</t>
+  </si>
+  <si>
+    <t>CANAPEA SORIA DUBLA</t>
+  </si>
+  <si>
+    <t>00013286  CANAPEA SORIA DUBLA</t>
+  </si>
+  <si>
+    <t>CANAPEA-SORIA-FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA SORIA FIXA</t>
+  </si>
+  <si>
+    <t>00009467  CANAPEA SORIA FIXA</t>
+  </si>
+  <si>
     <t>CANAPEA-SORINA</t>
   </si>
   <si>
@@ -157,6 +331,24 @@
     <t>00013664  CANAPEA SPRING</t>
   </si>
   <si>
+    <t>CANAPEA-TORRO</t>
+  </si>
+  <si>
+    <t>CANAPEA TORRO</t>
+  </si>
+  <si>
+    <t>00018649  CANAPEA TORRO</t>
+  </si>
+  <si>
+    <t>CANAPEA-TORRO-2L-FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA TORRO 2L FIXA</t>
+  </si>
+  <si>
+    <t>00024358  CANAPEA TORRO 2L FIXA</t>
+  </si>
+  <si>
     <t>CANAPEA-VISION</t>
   </si>
   <si>
@@ -166,52 +358,106 @@
     <t>00004970  CANAPEA VISION</t>
   </si>
   <si>
-    <t>CL-ECO</t>
-  </si>
-  <si>
-    <t>COLȚAR ECO</t>
+    <t>CANAPEA-VISION-FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA VISION FIXA</t>
+  </si>
+  <si>
+    <t>00007678  CANAPEA VISION FIXA</t>
+  </si>
+  <si>
+    <t>CANAPEA-VISION-II</t>
+  </si>
+  <si>
+    <t>CANAPEA VISION II</t>
+  </si>
+  <si>
+    <t>00006792  CANAPEA VISION II</t>
+  </si>
+  <si>
+    <t>COLTAR-ALDA</t>
+  </si>
+  <si>
+    <t>COLTAR ALDA</t>
   </si>
   <si>
     <t>COLTAR</t>
   </si>
   <si>
-    <t>00010380  COLTAR ECO II</t>
-  </si>
-  <si>
-    <t>CL-ROBERT</t>
-  </si>
-  <si>
-    <t>CL ROBERT</t>
-  </si>
-  <si>
-    <t>CL-ROBERT-7-PIESE</t>
-  </si>
-  <si>
-    <t>CL ROBERT 7 PIESE</t>
-  </si>
-  <si>
-    <t>CL-SORIA</t>
-  </si>
-  <si>
-    <t>CL SORIA</t>
-  </si>
-  <si>
-    <t>CL-TORRO-CU-KIT-POLIURETAN</t>
-  </si>
-  <si>
-    <t>CL TORRO (CU KIT POLIURETAN)</t>
-  </si>
-  <si>
-    <t>CL-TORRO-PROTOTIP</t>
-  </si>
-  <si>
-    <t>CL TORRO PROTOTIP</t>
-  </si>
-  <si>
-    <t>CL-VISION</t>
-  </si>
-  <si>
-    <t>CL VISION</t>
+    <t>00024585  COLTAR ALDA</t>
+  </si>
+  <si>
+    <t>COLTAR-ALDO</t>
+  </si>
+  <si>
+    <t>COLTAR ALDO</t>
+  </si>
+  <si>
+    <t>00021209  COLTAR ALDO</t>
+  </si>
+  <si>
+    <t>COLTAR-ALDO-U</t>
+  </si>
+  <si>
+    <t>COLTAR ALDO U</t>
+  </si>
+  <si>
+    <t>00022925  COLTAR ALDO U</t>
+  </si>
+  <si>
+    <t>COLTAR-ALEX</t>
+  </si>
+  <si>
+    <t>COLTAR ALEX</t>
+  </si>
+  <si>
+    <t>00000200  COLTAR ALEX</t>
+  </si>
+  <si>
+    <t>COLTAR-CHESTERFIELD</t>
+  </si>
+  <si>
+    <t>COLTAR CHESTERFIELD</t>
+  </si>
+  <si>
+    <t>00007148  COLTAR CHESTERFIELD</t>
+  </si>
+  <si>
+    <t>COLTAR-ECO</t>
+  </si>
+  <si>
+    <t>COLTAR ECO</t>
+  </si>
+  <si>
+    <t>00001646  COLTAR ECO</t>
+  </si>
+  <si>
+    <t>COLTAR-ECO-E-M</t>
+  </si>
+  <si>
+    <t>COLTAR ECO E+M</t>
+  </si>
+  <si>
+    <t>00004908  COLTAR ECO E+M</t>
+  </si>
+  <si>
+    <t>COLTAR-ECO-II-E-M-2000-2500</t>
+  </si>
+  <si>
+    <t>COLTAR ECO II E+M 2000/2500</t>
+  </si>
+  <si>
+    <t>00025110  COLTAR ECO II E+M 2000/2500</t>
+  </si>
+  <si>
+    <t>COLTAR-ECO-II-R-M</t>
+  </si>
+  <si>
+    <t>COLTAR ECO II R/M</t>
+  </si>
+  <si>
+    <t>00016684  COLTAR ECO II R/M</t>
   </si>
   <si>
     <t>COLTAR-ECO-R-M</t>
@@ -223,6 +469,81 @@
     <t>00004926  COLTAR ECO R+M</t>
   </si>
   <si>
+    <t>COLTAR-MONA</t>
+  </si>
+  <si>
+    <t>COLTAR MONA</t>
+  </si>
+  <si>
+    <t>00006784  COLTAR MONA</t>
+  </si>
+  <si>
+    <t>COLTAR-ROBERT-5-PIESE</t>
+  </si>
+  <si>
+    <t>COLTAR ROBERT 5 PIESE</t>
+  </si>
+  <si>
+    <t>00005879  COLTAR ROBERT 5 PIESE</t>
+  </si>
+  <si>
+    <t>COLTAR-ROBERT-7-PIESE</t>
+  </si>
+  <si>
+    <t>COLTAR ROBERT 7 PIESE</t>
+  </si>
+  <si>
+    <t>00005772  COLTAR ROBERT 7 PIESE</t>
+  </si>
+  <si>
+    <t>COLTAR-SORIA</t>
+  </si>
+  <si>
+    <t>COLTAR SORIA</t>
+  </si>
+  <si>
+    <t>00008642  COLTAR SORIA</t>
+  </si>
+  <si>
+    <t>COLTAR-SORIA-U</t>
+  </si>
+  <si>
+    <t>COLTAR SORIA U</t>
+  </si>
+  <si>
+    <t>00017704  COLTAR SORIA U</t>
+  </si>
+  <si>
+    <t>COLTAR-TORRO</t>
+  </si>
+  <si>
+    <t>COLTAR TORRO</t>
+  </si>
+  <si>
+    <t>00017073  COLTAR TORRO</t>
+  </si>
+  <si>
+    <t>COLTAR-TORRO-CU-KIT-POLIURETAN</t>
+  </si>
+  <si>
+    <t>COLTAR TORRO (CU KIT POLIURETAN)</t>
+  </si>
+  <si>
+    <t>COLTAR-TORRO-PROTOTIP</t>
+  </si>
+  <si>
+    <t>COLTAR TORRO PROTOTIP</t>
+  </si>
+  <si>
+    <t>COLTAR-VISION</t>
+  </si>
+  <si>
+    <t>COLTAR VISION</t>
+  </si>
+  <si>
+    <t>00000339  COLTAR VISION</t>
+  </si>
+  <si>
     <t>FOTOLIU-CORINA</t>
   </si>
   <si>
@@ -232,6 +553,18 @@
     <t>ALTELE</t>
   </si>
   <si>
+    <t>00000202  FOTOLIU CORINA</t>
+  </si>
+  <si>
+    <t>FOTOLIU-CORINA-II</t>
+  </si>
+  <si>
+    <t>FOTOLIU CORINA II</t>
+  </si>
+  <si>
+    <t>00000255  FOTOLIU CORINA II</t>
+  </si>
+  <si>
     <t>FOTOLIU-CORINA-II-EXTENSIBIL</t>
   </si>
   <si>
@@ -247,31 +580,178 @@
     <t>00000388  FOTOLIU KIM</t>
   </si>
   <si>
+    <t>FOTOLIU-SORIA-EXT</t>
+  </si>
+  <si>
+    <t>FOTOLIU SORIA EXT</t>
+  </si>
+  <si>
+    <t>00020264  FOTOLIU SORIA EXT</t>
+  </si>
+  <si>
+    <t>FOTOLIU-SORIA-FIX</t>
+  </si>
+  <si>
+    <t>FOTOLIU SORIA FIX</t>
+  </si>
+  <si>
+    <t>00020218  FOTOLIU SORIA FIX</t>
+  </si>
+  <si>
+    <t>FOTOLIU-SORINA-II</t>
+  </si>
+  <si>
+    <t>FOTOLIU SORINA II</t>
+  </si>
+  <si>
+    <t>00012200  FOTOLIU SORINA II</t>
+  </si>
+  <si>
+    <t>FOTOLIU-VISION-EXT</t>
+  </si>
+  <si>
+    <t>FOTOLIU VISION EXT.</t>
+  </si>
+  <si>
+    <t>00006616  FOTOLIU VISION EXT.</t>
+  </si>
+  <si>
+    <t>FOTOLIU-VISION-FIX</t>
+  </si>
+  <si>
+    <t>FOTOLIU VISION FIX</t>
+  </si>
+  <si>
+    <t>00015190  FOTOLIU VISION FIX</t>
+  </si>
+  <si>
     <t>FOTOLIU-VISION-II-EXTENSIBIL</t>
   </si>
   <si>
     <t>FOTOLIU VISION II EXTENSIBIL</t>
   </si>
   <si>
+    <t>HOL-CORINA</t>
+  </si>
+  <si>
+    <t>HOL CORINA</t>
+  </si>
+  <si>
+    <t>00000262  HOL CORINA</t>
+  </si>
+  <si>
     <t>HOL-CORINA-311</t>
   </si>
   <si>
     <t>HOL CORINA 3.1.1. FOTOLII EXTENSIBILE</t>
   </si>
   <si>
+    <t>00005835  HOL CORINA 3.1.1.</t>
+  </si>
+  <si>
+    <t>HOL-CORINA-II</t>
+  </si>
+  <si>
+    <t>HOL CORINA II</t>
+  </si>
+  <si>
+    <t>00002857  HOL CORINA II</t>
+  </si>
+  <si>
     <t>HOL-VISION-311</t>
   </si>
   <si>
     <t>HOL VISION 3.1.1. FOTOLII EXTENSIBILE</t>
   </si>
   <si>
+    <t>00006940  HOL VISION 3.1.1.</t>
+  </si>
+  <si>
+    <t>MOBILIER</t>
+  </si>
+  <si>
+    <t>00000793  MOBILIER</t>
+  </si>
+  <si>
+    <t>PAT-ALDO-1400-2000</t>
+  </si>
+  <si>
+    <t>PAT ALDO 1400/2000</t>
+  </si>
+  <si>
+    <t>PAT</t>
+  </si>
+  <si>
+    <t>00024791  PAT ALDO 1400/2000</t>
+  </si>
+  <si>
+    <t>PAT-BUCLE-VERICALE-1600-2000</t>
+  </si>
+  <si>
+    <t>PAT BUCLE VERICALE 1600/2000</t>
+  </si>
+  <si>
+    <t>00023467  PAT BUCLE VERICALE 1600/2000</t>
+  </si>
+  <si>
+    <t>PAT-CAMERA-TINERET-1400-1900</t>
+  </si>
+  <si>
+    <t>PAT CAMERA TINERET 1400/1900</t>
+  </si>
+  <si>
+    <t>00021568  PAT CAMERA TINERET 1400/1900</t>
+  </si>
+  <si>
     <t>PAT-CHESTERFIELD-2000X1600-CU-SOMIERA</t>
   </si>
   <si>
     <t>PAT CHESTERFIELD 2000x1600 CU SOMIERA</t>
   </si>
   <si>
-    <t>PAT</t>
+    <t>PAT-CHESTERFIELD-FARA-SATOZA</t>
+  </si>
+  <si>
+    <t>PAT CHESTERFIELD FARA SATOZA</t>
+  </si>
+  <si>
+    <t>00025122  PAT CHESTERFIELD FARA SATOZA 1600/2000</t>
+  </si>
+  <si>
+    <t>PAT-COLT-1200-2000</t>
+  </si>
+  <si>
+    <t>PAT COLT 1200/2000</t>
+  </si>
+  <si>
+    <t>00025246  PAT COLT 1200/2000</t>
+  </si>
+  <si>
+    <t>PAT-DAN-1400-2000</t>
+  </si>
+  <si>
+    <t>PAT DAN 1400/2000</t>
+  </si>
+  <si>
+    <t>00017495  PAT DAN 1400/2000</t>
+  </si>
+  <si>
+    <t>PAT-DAN-1600-2000</t>
+  </si>
+  <si>
+    <t>PAT DAN 1600/2000</t>
+  </si>
+  <si>
+    <t>00017799  PAT DAN 1600/2000</t>
+  </si>
+  <si>
+    <t>PAT-DAVID-1400-1900</t>
+  </si>
+  <si>
+    <t>PAT DAVID 1400/1900</t>
+  </si>
+  <si>
+    <t>00001779  PAT DAVID 1400/1900</t>
   </si>
   <si>
     <t>PAT-DAVID-2000X1400</t>
@@ -280,10 +760,118 @@
     <t>PAT DAVID 2000X1400 (saltea incorporata)</t>
   </si>
   <si>
+    <t>00001654  PAT DAVID 1400/2000</t>
+  </si>
+  <si>
+    <t>PAT-FANTEZIE-1600-2000</t>
+  </si>
+  <si>
+    <t>PAT FANTEZIE 1600/2000</t>
+  </si>
+  <si>
+    <t>00021195  PAT FANTEZIE 1600/2000</t>
+  </si>
+  <si>
+    <t>PAT-FORME-GEOMETRICE-2000-1400</t>
+  </si>
+  <si>
+    <t>PAT FORME GEOMETRICE 2000/1400</t>
+  </si>
+  <si>
+    <t>00021487  PAT FORME GEOMETRICE 2000/1400</t>
+  </si>
+  <si>
+    <t>PAT-GARDULET-1200-2000</t>
+  </si>
+  <si>
+    <t>PAT GARDULET 1200/2000</t>
+  </si>
+  <si>
+    <t>00023110  PAT GARDULET 1200/2000</t>
+  </si>
+  <si>
+    <t>PAT-IEPURAS-CU-SOFA-1400-1900</t>
+  </si>
+  <si>
+    <t>PAT IEPURAS CU SOFA 1400/1900</t>
+  </si>
+  <si>
+    <t>00024793  PAT IEPURAS CU SOFA 1400/1900</t>
+  </si>
+  <si>
+    <t>PAT-MIRAJ-1400-2000</t>
+  </si>
+  <si>
+    <t>PAT MIRAJ 1400/2000</t>
+  </si>
+  <si>
+    <t>00022496  PAT MIRAJ 1400/2000</t>
+  </si>
+  <si>
+    <t>PAT-PAUL-2-1-4</t>
+  </si>
+  <si>
+    <t>PAT PAUL 2/1.4</t>
+  </si>
+  <si>
+    <t>00013356  PAT PAUL 2/1.4</t>
+  </si>
+  <si>
     <t>PAT-PAUL-2000X1600-CU-SOMIERA</t>
   </si>
   <si>
     <t>PAT PAUL 2000x1600 CU SOMIERA</t>
+  </si>
+  <si>
+    <t>00025134  PAT PAUL SOMIERA 2000/1600</t>
+  </si>
+  <si>
+    <t>PAT-SUN-1600-2000</t>
+  </si>
+  <si>
+    <t>PAT SUN 1600/2000</t>
+  </si>
+  <si>
+    <t>00021504  PAT SUN 1600/2000</t>
+  </si>
+  <si>
+    <t>SALTEA-E-M-1400-2000</t>
+  </si>
+  <si>
+    <t>SALTEA E+M 1400/2000</t>
+  </si>
+  <si>
+    <t>SALTEA</t>
+  </si>
+  <si>
+    <t>00020002  SALTEA E+M 1400/2000</t>
+  </si>
+  <si>
+    <t>SALTEA-R-M-1400-2000</t>
+  </si>
+  <si>
+    <t>SALTEA R+M 1400/2000</t>
+  </si>
+  <si>
+    <t>00020830  SALTEA R+M 1400/2000</t>
+  </si>
+  <si>
+    <t>TABURET-40-40</t>
+  </si>
+  <si>
+    <t>TABURET 40/40</t>
+  </si>
+  <si>
+    <t>00002032  TABURET 40/40</t>
+  </si>
+  <si>
+    <t>TABURET-ALDO</t>
+  </si>
+  <si>
+    <t>TABURET ALDO</t>
+  </si>
+  <si>
+    <t>00023356  TABURET ALDO</t>
   </si>
   <si>
     <t>TABURETE</t>
@@ -675,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -742,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="E2" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1">
-        <v>1900</v>
-      </c>
-      <c r="G2" s="1">
-        <v>350</v>
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1500</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1900</v>
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -771,28 +1359,28 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>900</v>
-      </c>
-      <c r="G3" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>17</v>
@@ -804,36 +1392,36 @@
         <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>900</v>
-      </c>
-      <c r="G4" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>17</v>
@@ -845,7 +1433,7 @@
         <v>17</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -853,16 +1441,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1">
         <v>2000</v>
@@ -874,7 +1462,7 @@
         <v>850</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>17</v>
@@ -886,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -894,16 +1482,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
         <v>2000</v>
@@ -915,7 +1503,7 @@
         <v>850</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>17</v>
@@ -927,36 +1515,36 @@
         <v>17</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>900</v>
-      </c>
-      <c r="G7" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>17</v>
@@ -968,36 +1556,36 @@
         <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>900</v>
-      </c>
-      <c r="G8" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
@@ -1009,7 +1597,7 @@
         <v>17</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1017,16 +1605,16 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1">
         <v>2000</v>
@@ -1038,7 +1626,7 @@
         <v>850</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>17</v>
@@ -1050,7 +1638,7 @@
         <v>17</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -1058,28 +1646,28 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>1600</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>17</v>
@@ -1091,7 +1679,7 @@
         <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1099,28 +1687,28 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>900</v>
-      </c>
-      <c r="G11" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>17</v>
@@ -1132,24 +1720,24 @@
         <v>17</v>
       </c>
       <c r="L11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1">
         <v>2000</v>
@@ -1161,7 +1749,7 @@
         <v>850</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>17</v>
@@ -1173,7 +1761,7 @@
         <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1181,28 +1769,28 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>900</v>
-      </c>
-      <c r="G13" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>17</v>
@@ -1214,7 +1802,7 @@
         <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1222,28 +1810,28 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>900</v>
-      </c>
-      <c r="G14" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>17</v>
@@ -1255,7 +1843,7 @@
         <v>17</v>
       </c>
       <c r="L14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1263,28 +1851,28 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="F15" s="1">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="G15" s="1">
         <v>850</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>17</v>
@@ -1296,7 +1884,7 @@
         <v>17</v>
       </c>
       <c r="L15" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1304,28 +1892,28 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G16" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>17</v>
@@ -1337,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1345,28 +1933,28 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G17" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>17</v>
@@ -1378,7 +1966,7 @@
         <v>17</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1386,28 +1974,28 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G18" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>17</v>
@@ -1419,7 +2007,7 @@
         <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1427,28 +2015,28 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="F19" s="1">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="G19" s="1">
         <v>850</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>17</v>
@@ -1460,7 +2048,7 @@
         <v>17</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -1468,28 +2056,28 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G20" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>17</v>
@@ -1501,7 +2089,7 @@
         <v>17</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1509,28 +2097,28 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="F21" s="1">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="G21" s="1">
         <v>850</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>17</v>
@@ -1542,36 +2130,36 @@
         <v>17</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G22" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>17</v>
@@ -1583,7 +2171,7 @@
         <v>17</v>
       </c>
       <c r="L22" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1591,28 +2179,28 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>600</v>
-      </c>
-      <c r="G23" s="1">
-        <v>450</v>
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>17</v>
@@ -1624,7 +2212,7 @@
         <v>17</v>
       </c>
       <c r="L23" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1632,28 +2220,28 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>600</v>
-      </c>
-      <c r="G24" s="1">
-        <v>450</v>
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>17</v>
@@ -1665,7 +2253,7 @@
         <v>17</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1673,28 +2261,28 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="F25" s="1">
-        <v>600</v>
-      </c>
-      <c r="G25" s="1">
-        <v>450</v>
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>17</v>
@@ -1706,7 +2294,7 @@
         <v>17</v>
       </c>
       <c r="L25" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1714,28 +2302,28 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="F26" s="1">
-        <v>600</v>
-      </c>
-      <c r="G26" s="1">
-        <v>450</v>
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>17</v>
@@ -1747,7 +2335,7 @@
         <v>17</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -1755,28 +2343,28 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F27" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G27" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>17</v>
@@ -1788,7 +2376,7 @@
         <v>17</v>
       </c>
       <c r="L27" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -1796,28 +2384,28 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E28" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
       <c r="F28" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G28" s="1">
-        <v>850</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>17</v>
@@ -1829,7 +2417,7 @@
         <v>17</v>
       </c>
       <c r="L28" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -1837,40 +2425,40 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E29" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1600</v>
-      </c>
-      <c r="G29" s="1">
-        <v>350</v>
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1600</v>
+        <v>18</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1878,40 +2466,40 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E30" s="1">
         <v>2000</v>
       </c>
       <c r="F30" s="1">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="G30" s="1">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1400</v>
+        <v>18</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L30" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -1919,40 +2507,40 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E31" s="1">
         <v>2000</v>
       </c>
       <c r="F31" s="1">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="G31" s="1">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1600</v>
+        <v>18</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -1960,42 +2548,2543 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" t="s">
+        <v>108</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" t="s">
+        <v>111</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F34" s="1">
+        <v>900</v>
+      </c>
+      <c r="G34" s="1">
+        <v>850</v>
+      </c>
+      <c r="H34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34" t="s">
+        <v>114</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" t="s">
+        <v>117</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" t="s">
+        <v>120</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37" t="s">
+        <v>124</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38" t="s">
+        <v>127</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" t="s">
+        <v>130</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40" t="s">
+        <v>133</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" t="s">
+        <v>136</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" t="s">
+        <v>139</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" t="s">
+        <v>142</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J44" s="1">
+        <v>2500</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" t="s">
+        <v>145</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" t="s">
+        <v>148</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G46" s="1">
+        <v>850</v>
+      </c>
+      <c r="H46" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" t="s">
+        <v>151</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" t="s">
+        <v>154</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" t="s">
+        <v>157</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" t="s">
+        <v>160</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" t="s">
+        <v>163</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" t="s">
+        <v>166</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" t="s">
+        <v>123</v>
+      </c>
+      <c r="D52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" t="s">
+        <v>169</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G53" s="1">
+        <v>850</v>
+      </c>
+      <c r="H53" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" t="s">
+        <v>169</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G54" s="1">
+        <v>850</v>
+      </c>
+      <c r="H54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" t="s">
+        <v>169</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" t="s">
+        <v>176</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" t="s">
+        <v>179</v>
+      </c>
+      <c r="D56" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="1">
         <v>600</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F56" s="1">
         <v>600</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G56" s="1">
         <v>450</v>
       </c>
-      <c r="H32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L32" t="s">
-        <v>93</v>
-      </c>
-      <c r="M32">
+      <c r="H56" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L56" t="s">
+        <v>180</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" t="s">
+        <v>183</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="1">
+        <v>600</v>
+      </c>
+      <c r="F58" s="1">
+        <v>600</v>
+      </c>
+      <c r="G58" s="1">
+        <v>450</v>
+      </c>
+      <c r="H58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L58" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" t="s">
+        <v>187</v>
+      </c>
+      <c r="C59" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="1">
+        <v>600</v>
+      </c>
+      <c r="F59" s="1">
+        <v>600</v>
+      </c>
+      <c r="G59" s="1">
+        <v>450</v>
+      </c>
+      <c r="H59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" t="s">
+        <v>188</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" t="s">
+        <v>191</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L61" t="s">
+        <v>194</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" t="s">
+        <v>196</v>
+      </c>
+      <c r="C62" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" t="s">
+        <v>197</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" t="s">
+        <v>199</v>
+      </c>
+      <c r="C63" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L63" t="s">
+        <v>200</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>201</v>
+      </c>
+      <c r="B64" t="s">
+        <v>202</v>
+      </c>
+      <c r="C64" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" t="s">
+        <v>203</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>204</v>
+      </c>
+      <c r="B65" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" t="s">
+        <v>179</v>
+      </c>
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="1">
+        <v>600</v>
+      </c>
+      <c r="F65" s="1">
+        <v>600</v>
+      </c>
+      <c r="G65" s="1">
+        <v>450</v>
+      </c>
+      <c r="H65" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L65" t="s">
+        <v>28</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>206</v>
+      </c>
+      <c r="B66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66" t="s">
+        <v>208</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>209</v>
+      </c>
+      <c r="B67" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G67" s="1">
+        <v>850</v>
+      </c>
+      <c r="H67" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L67" t="s">
+        <v>211</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" t="s">
+        <v>179</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H68" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L68" t="s">
+        <v>214</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" t="s">
+        <v>216</v>
+      </c>
+      <c r="C69" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G69" s="1">
+        <v>850</v>
+      </c>
+      <c r="H69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L69" t="s">
+        <v>217</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>218</v>
+      </c>
+      <c r="B70" t="s">
+        <v>218</v>
+      </c>
+      <c r="C70" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L70" t="s">
+        <v>219</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>220</v>
+      </c>
+      <c r="B71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" t="s">
+        <v>222</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H71" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J71" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L71" t="s">
+        <v>223</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>224</v>
+      </c>
+      <c r="B72" t="s">
+        <v>225</v>
+      </c>
+      <c r="C72" t="s">
+        <v>222</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1600</v>
+      </c>
+      <c r="J72" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" t="s">
+        <v>226</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>227</v>
+      </c>
+      <c r="B73" t="s">
+        <v>228</v>
+      </c>
+      <c r="C73" t="s">
+        <v>222</v>
+      </c>
+      <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1900</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L73" t="s">
+        <v>229</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>230</v>
+      </c>
+      <c r="B74" t="s">
+        <v>231</v>
+      </c>
+      <c r="C74" t="s">
+        <v>222</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1600</v>
+      </c>
+      <c r="G74" s="1">
+        <v>350</v>
+      </c>
+      <c r="H74" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1600</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L74" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>232</v>
+      </c>
+      <c r="B75" t="s">
+        <v>233</v>
+      </c>
+      <c r="C75" t="s">
+        <v>222</v>
+      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1600</v>
+      </c>
+      <c r="J75" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L75" t="s">
+        <v>234</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>235</v>
+      </c>
+      <c r="B76" t="s">
+        <v>236</v>
+      </c>
+      <c r="C76" t="s">
+        <v>222</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1200</v>
+      </c>
+      <c r="J76" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" t="s">
+        <v>237</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" t="s">
+        <v>239</v>
+      </c>
+      <c r="C77" t="s">
+        <v>222</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J77" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77" t="s">
+        <v>240</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>241</v>
+      </c>
+      <c r="B78" t="s">
+        <v>242</v>
+      </c>
+      <c r="C78" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="1">
+        <v>1600</v>
+      </c>
+      <c r="J78" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" t="s">
+        <v>243</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>244</v>
+      </c>
+      <c r="B79" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" t="s">
+        <v>222</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1900</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79" t="s">
+        <v>246</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>247</v>
+      </c>
+      <c r="B80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C80" t="s">
+        <v>222</v>
+      </c>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1600</v>
+      </c>
+      <c r="G80" s="1">
+        <v>350</v>
+      </c>
+      <c r="H80" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1400</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80" t="s">
+        <v>249</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" t="s">
+        <v>222</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1600</v>
+      </c>
+      <c r="J81" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81" t="s">
+        <v>252</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>253</v>
+      </c>
+      <c r="B82" t="s">
+        <v>254</v>
+      </c>
+      <c r="C82" t="s">
+        <v>222</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1400</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L82" t="s">
+        <v>255</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>256</v>
+      </c>
+      <c r="B83" t="s">
+        <v>257</v>
+      </c>
+      <c r="C83" t="s">
+        <v>222</v>
+      </c>
+      <c r="D83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1200</v>
+      </c>
+      <c r="J83" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83" t="s">
+        <v>258</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>259</v>
+      </c>
+      <c r="B84" t="s">
+        <v>260</v>
+      </c>
+      <c r="C84" t="s">
+        <v>222</v>
+      </c>
+      <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" t="s">
+        <v>18</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1900</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L84" t="s">
+        <v>261</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>262</v>
+      </c>
+      <c r="B85" t="s">
+        <v>263</v>
+      </c>
+      <c r="C85" t="s">
+        <v>222</v>
+      </c>
+      <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J85" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85" t="s">
+        <v>264</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>265</v>
+      </c>
+      <c r="B86" t="s">
+        <v>266</v>
+      </c>
+      <c r="C86" t="s">
+        <v>222</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1400</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L86" t="s">
+        <v>267</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>268</v>
+      </c>
+      <c r="B87" t="s">
+        <v>269</v>
+      </c>
+      <c r="C87" t="s">
+        <v>222</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1600</v>
+      </c>
+      <c r="G87" s="1">
+        <v>350</v>
+      </c>
+      <c r="H87" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J87" s="1">
+        <v>1600</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L87" t="s">
+        <v>270</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>271</v>
+      </c>
+      <c r="B88" t="s">
+        <v>272</v>
+      </c>
+      <c r="C88" t="s">
+        <v>222</v>
+      </c>
+      <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" s="1">
+        <v>1600</v>
+      </c>
+      <c r="J88" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L88" t="s">
+        <v>273</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>274</v>
+      </c>
+      <c r="B89" t="s">
+        <v>275</v>
+      </c>
+      <c r="C89" t="s">
+        <v>276</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J89" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L89" t="s">
+        <v>277</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90" t="s">
+        <v>279</v>
+      </c>
+      <c r="C90" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" s="1">
+        <v>1400</v>
+      </c>
+      <c r="J90" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L90" t="s">
+        <v>280</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>281</v>
+      </c>
+      <c r="B91" t="s">
+        <v>282</v>
+      </c>
+      <c r="C91" t="s">
+        <v>179</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L91" t="s">
+        <v>283</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>284</v>
+      </c>
+      <c r="B92" t="s">
+        <v>285</v>
+      </c>
+      <c r="C92" t="s">
+        <v>179</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L92" t="s">
+        <v>286</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>287</v>
+      </c>
+      <c r="B93" t="s">
+        <v>288</v>
+      </c>
+      <c r="C93" t="s">
+        <v>179</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="1">
+        <v>600</v>
+      </c>
+      <c r="F93" s="1">
+        <v>600</v>
+      </c>
+      <c r="G93" s="1">
+        <v>450</v>
+      </c>
+      <c r="H93" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L93" t="s">
+        <v>289</v>
+      </c>
+      <c r="M93">
         <v>0</v>
       </c>
     </row>
